--- a/SGC-CKN/Excel/27a452c5-bfeb-4ac0-a46b-c1bb6f361c69_Thi_công_cọc_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P2-69_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/27a452c5-bfeb-4ac0-a46b-c1bb6f361c69_Thi_công_cọc_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P2-69_D800_06-04-2026.xlsx
@@ -109,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:05
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">15:20
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">17:05
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi, sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">18:00
@@ -159,24 +159,24 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:00
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:40
 05/04/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:30
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">23:15
+    <t xml:space="preserve">03:23
 06/04/2026</t>
   </si>
   <si>
@@ -217,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -290,12 +290,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -306,7 +300,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,11 +370,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -476,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -568,16 +557,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1271,16 +1257,16 @@
         <v>-7.9</v>
       </c>
       <c r="G14" s="15">
-        <v>-16.4</v>
+        <v>-16.1</v>
       </c>
       <c r="H14" s="15">
         <v>1.33</v>
       </c>
       <c r="I14" s="15">
-        <v>8.5</v>
+        <v>8.2</v>
       </c>
       <c r="J14" s="8">
-        <v>6.37</v>
+        <v>6.15</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>29</v>
@@ -1303,7 +1289,7 @@
         <v>41</v>
       </c>
       <c r="F15" s="18">
-        <v>-16.4</v>
+        <v>-16.1</v>
       </c>
       <c r="G15" s="18">
         <v>-22</v>
@@ -1312,10 +1298,10 @@
         <v>0.42</v>
       </c>
       <c r="I15" s="18">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J15" s="8">
-        <v>13.44</v>
+        <v>14.16</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>29</v>
@@ -1379,13 +1365,13 @@
         <v>-39</v>
       </c>
       <c r="H17" s="25">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="I17" s="25">
         <v>13</v>
       </c>
       <c r="J17" s="8">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>29</v>
@@ -1411,35 +1397,35 @@
         <v>-39</v>
       </c>
       <c r="G18" s="28">
-        <v>-39.4</v>
+        <v>-44.01</v>
       </c>
       <c r="H18" s="28">
-        <v>23.75</v>
+        <v>3.88</v>
       </c>
       <c r="I18" s="28">
-        <v>0.4</v>
-      </c>
-      <c r="J18" s="31">
-        <v>0.02</v>
+        <v>5.01</v>
+      </c>
+      <c r="J18" s="24">
+        <v>1.29</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1665,16 +1651,16 @@
         <v>-7.9</v>
       </c>
       <c r="F5" s="15">
-        <v>-16.4</v>
+        <v>-16.1</v>
       </c>
       <c r="G5" s="15">
         <v>1.33</v>
       </c>
       <c r="H5" s="15">
-        <v>8.5</v>
+        <v>8.2</v>
       </c>
       <c r="I5" s="8">
-        <v>6.37</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1691,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-16.4</v>
+        <v>-16.1</v>
       </c>
       <c r="F6" s="18">
         <v>-22</v>
@@ -1700,10 +1686,10 @@
         <v>0.42</v>
       </c>
       <c r="H6" s="18">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="8">
-        <v>13.44</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1755,13 +1741,13 @@
         <v>-39</v>
       </c>
       <c r="G8" s="25">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H8" s="25">
         <v>13</v>
       </c>
       <c r="I8" s="8">
-        <v>13</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,45 +1767,45 @@
         <v>-39</v>
       </c>
       <c r="F9" s="28">
-        <v>-39.4</v>
+        <v>-44.01</v>
       </c>
       <c r="G9" s="28">
-        <v>23.75</v>
+        <v>3.88</v>
       </c>
       <c r="H9" s="28">
-        <v>0.4</v>
-      </c>
-      <c r="I9" s="31">
-        <v>0.02</v>
+        <v>5.01</v>
+      </c>
+      <c r="I9" s="24">
+        <v>1.29</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
-        <v>-39.4</v>
-      </c>
-      <c r="G10" s="34">
-        <v>28.25</v>
-      </c>
-      <c r="H10" s="34">
-        <v>39.4</v>
-      </c>
-      <c r="I10" s="34">
-        <v>1.39</v>
+      <c r="F10" s="33">
+        <v>-44.01</v>
+      </c>
+      <c r="G10" s="33">
+        <v>9.05</v>
+      </c>
+      <c r="H10" s="33">
+        <v>44.01</v>
+      </c>
+      <c r="I10" s="33">
+        <v>4.86</v>
       </c>
     </row>
   </sheetData>
